--- a/executive_emails.xlsx
+++ b/executive_emails.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J516"/>
+  <dimension ref="A1:J628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26234,6 +26234,5606 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>samantha.forney@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Samantha</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Forney</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Sales Operations Director</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>99</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>lauren.eonta@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Eonta</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Director of Sales</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>99</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>amanda.zylka@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Zylka</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Commercial Strategy Director</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>99</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>johannis.siahaya@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Johannis</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Siahaya</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Head of Logistics</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>99</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>sergio.godinez@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Sergio</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Godinez</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>99</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>elle.atton@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Elle</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Atton</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Marketing Insights Director</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>99</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>stephanie.nahhat@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Nahhat</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Senior Director of Human Resources</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>99</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>molly.matson@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Molly</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Matson</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Director of Sports Marketing</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>99</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>pepsico.com</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>javier.rodriguez@pepsico.com</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Javier</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Director of Route Planning and Design</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>99</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>jessica.amt@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>Amt</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Manufacturing Director</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>99</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>nathan.hollar@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Nathan</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>Hollar</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>99</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>cheryl.plasterer@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Cheryl</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>Plasterer</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Director of Forecasting</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>99</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>ryan.bauserman@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>Bauserman</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Director of Integration</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>99</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>jennifer.vogel@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>Vogel</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Director, Supply Chain</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>99</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>amy.wehr@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Amy</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Wehr</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Chief of Staff</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>98</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>tony.allen@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Director of Customer Experience</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>98</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>lauren.schneider@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Lauren</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>Schneider</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>98</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>francisco.navarro@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Navarro</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Labor Management Director</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>98</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>fritolay.com</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Frito-Lay</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>nicholas.powell@fritolay.com</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Nicholas</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Powell</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>97</v>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>michael.jantzen@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Jantzen</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Supply Chain Finance Director</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>99</v>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>jeremy.reese@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Jeremy</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Reese</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Vice President of Finance</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>99</v>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>ben.irby@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Irby</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>99</v>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>alli.jones@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Alli</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Director of Animal Protein</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>99</v>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>rafael.andrade@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Andrade</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>99</v>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>doreen.thomas@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Doreen</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Head of Sourcing</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>99</v>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>emily.deacon@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Deacon</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Director of Customer Experience</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>99</v>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>aimee.wilford@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Aimee</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Wilford</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Vice President of Talent Strategy and Growth</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>99</v>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>generalmills.com</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>teressa.silverman@generalmills.com</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Teressa</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Silverman</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Director of Compensation</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>99</v>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Wise Foods</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>brian.musser@wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Brian</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Musser</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>National Director of Key Accounts</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>93</v>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Wise Foods</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>kathryn.mariani@wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Kathryn</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>Mariani</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Director of National Accounts</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>93</v>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Wise Foods</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>mike.ellis@wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Ellis</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Director of Sales and Operations</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>92</v>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Wise Foods</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>david.protheroe@wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Protheroe</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>92</v>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Wise Foods</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>william.mcknight@wisesnacks.com</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>McKnight</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>91</v>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>laura.turnbull@graze.com</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Turnbull</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Director of Transformation</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>94</v>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>eleanor.mcclelland@graze.com</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Eleanor</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>McClelland</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Director of Research and Development</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>94</v>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>claire.simpson@graze.com</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Claire</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Simpson</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Director of Manufacturing</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>93</v>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>andy.robinson@graze.com</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Andy</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Robinson</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>92</v>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>adam.flores@graze.com</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>IT Director</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>91</v>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>scott.culcheth@graze.com</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Culcheth</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Chief Architect</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>82</v>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>graze.com</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Graze</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>dorina.mazilu@graze.com</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Dorina</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Mazilu</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Testing Coordinator</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>94</v>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>calbee.co.jp</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Calbee</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>k_tanabe@calbee.co.jp</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Kazuhiro</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Tanabe</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>98</v>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>calbee.co.jp</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Calbee</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>s_haruna@calbee.co.jp</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Shinji</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Haruna</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Executive Vice President, General Manager</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>98</v>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>sara@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Berman</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Senior Director of Brand Experience</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>99</v>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>adam@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Hauser</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Vice President of Finance</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>99</v>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>hilary@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Hilary</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Bañales</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Vice President of Manufacturing</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>98</v>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>erika@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Erika</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Allen-Walsh</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Executive Vice President of Marketing</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>98</v>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>ericle@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Le</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Senior Director of Growth Marketing</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>98</v>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>ricardo@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Ricardo</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Director of Research and Development</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>97</v>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>jenna@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Jenna</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Vice President of Supply Chain</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>97</v>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>kathy@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Kathy</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Elefano</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Executive Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>97</v>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>veronica@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Veronica</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Garza</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>97</v>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>sietefoods.com</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Siete Foods</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>andrea@sietefoods.com</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>96</v>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>jdutcher@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Dutcher</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Sales Operations Director</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>99</v>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>lfitzgerald@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Fitzgerald</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Director of Research and Development</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>99</v>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>chwang@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Cristy</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Hwang</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Senior Director of Finance</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>99</v>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>jrock@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Director of Finance</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>99</v>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>mnasta@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Mohit</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Nasta</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Senior Finance Director</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>99</v>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>kdiggins@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Kelly</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Diggins</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Vice President of Legal Affairs</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>99</v>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>kmorris@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Keith</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Director of Sales Operations</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>99</v>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>rlangley@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Langley</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Procurement Director</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>99</v>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>enichols@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Earl</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Nichols</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Director of Quality</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>99</v>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Utz Brands</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>ayeager@utzsnacks.com</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Yeager</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Vice President of Integrated Business Management</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>99</v>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>casey.slone@herrs.com</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Slone</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Vice President, Partner Brands</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>94</v>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>kelli.strohmaier@herrs.com</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Kelli</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Strohmaier</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Director of IT Infrastructure</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>94</v>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>scott.bailey@herrs.com</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Bailey</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H581" t="n">
+        <v>94</v>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>stacy.zeager@herrs.com</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Stacy</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Zeager</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Senior Vice President of Human Resources</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>93</v>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>jim.herr@herrs.com</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Herr</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Senior Vice President of Marketing</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>93</v>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>nick.cortese@herrs.com</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Cortese</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>92</v>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>eric.carmichael@herrs.com</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Carmichael</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Senior Director of Sales</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>92</v>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>eva.yarris@herrs.com</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Yarris</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Director of Business Intelligence</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>91</v>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>herrs.com</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Herr Foods</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>jim.rock@herrs.com</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Rock</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Vice President of Key Accounts</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H587" t="n">
+        <v>91</v>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>partakefoods.com</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Partake Foods</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>kaleb@partakefoods.com</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Kaleb</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Loftus</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Ecommerce Director</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H588" t="n">
+        <v>99</v>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>partakefoods.com</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Partake Foods</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>tyler@partakefoods.com</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Davidov</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Director of National Accounts</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>99</v>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>partakefoods.com</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Partake Foods</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>kent@partakefoods.com</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Seger</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Head of Quality Assurance</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>99</v>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>partakefoods.com</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Partake Foods</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>denise@partakefoods.com</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Denise</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Woodard</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>97</v>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>partakefoods.com</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Partake Foods</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>ian@partakefoods.com</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Beert</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Vice President of Operations</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>96</v>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>manny@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Manny</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Arthur</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Art Director</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>99</v>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>coreyb@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Corey</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Director of Sales</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>99</v>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>ryan@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Barrios</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H595" t="n">
+        <v>98</v>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>andrew@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Strife</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>97</v>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>mike@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>97</v>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>monina@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Monina</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Manuel</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>96</v>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>lesserevil.com</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>LesserEvil</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>josh@lesserevil.com</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Antelo</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>96</v>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>barnana.com</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Barnana</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>nik@barnana.com</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Nik</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Ingersöll</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>99</v>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>barnana.com</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Barnana</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>price@barnana.com</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Vice President of Operations</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>98</v>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>tom@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Dikeman</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Director of Foodservice</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>94</v>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>fallon@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Fallon</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Halloran</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>94</v>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>donald@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Donald</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Ladouceur</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H604" t="n">
+        <v>93</v>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>chris@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Weaver</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H605" t="n">
+        <v>93</v>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>cesar@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>César</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Melo</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H606" t="n">
+        <v>92</v>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>steve@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Viles</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Executive Vice President of Sales</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H607" t="n">
+        <v>91</v>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>ankur@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Ankur</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Agrawal</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H608" t="n">
+        <v>90</v>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>nmarmet@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Marmet</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Director of E-commerce</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H609" t="n">
+        <v>89</v>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>mdamkot@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Damkot</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H610" t="n">
+        <v>84</v>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>hippeas.com</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>HIPPEAS</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>brendan@hippeas.com</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Brendan</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Graham</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H611" t="n">
+        <v>67</v>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>francisco.blanco@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Francisco</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Blanco</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H612" t="n">
+        <v>94</v>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>kenneth.ziegler@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Kenneth</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Ziegler</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>HR Director</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H613" t="n">
+        <v>94</v>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>paul.gingrich@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Gingrich</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Director of Distribution</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H614" t="n">
+        <v>94</v>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>sebastian.genesio@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Genesio</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Marketing Director</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>marketing</t>
+        </is>
+      </c>
+      <c r="H615" t="n">
+        <v>94</v>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>jim.cali@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Global Director of Gum and Candy</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H616" t="n">
+        <v>94</v>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>jimmy.murphy@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Jimmy</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Murphy</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Account Director</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H617" t="n">
+        <v>94</v>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>raj.rana@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Rana</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H618" t="n">
+        <v>94</v>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>anil.yadav@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Anil</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Yadav</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Chief Data Officer</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H619" t="n">
+        <v>93</v>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>cadbury.com</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Cadbury Adams</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>norma.skolnik@cadbury.com</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Norma</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Skolnik</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Director of Regulatory Affairs</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H620" t="n">
+        <v>93</v>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>sara.tastan@haribo.com</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Tastan</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Assistant Vice President of Operations</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H621" t="n">
+        <v>99</v>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>murat.demirtas@haribo.com</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Murat</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Demirtas</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H622" t="n">
+        <v>99</v>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>ayhan.epdenli@haribo.com</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Ayhan</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Epdenli</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Director of Finance</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="H623" t="n">
+        <v>99</v>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>drew.williams@haribo.com</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Director of Talent Acquisition</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H624" t="n">
+        <v>99</v>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>ekta.mahajan@haribo.com</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Ekta</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Mahajan</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Supply Chain Director</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="H625" t="n">
+        <v>99</v>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>onur.mermer@haribo.com</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Onur</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Mermer</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Regional Sales Director</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="H626" t="n">
+        <v>99</v>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>edgar.christen@haribo.com</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Edgar</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Christen</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Supply Chain Director</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>operations</t>
+        </is>
+      </c>
+      <c r="H627" t="n">
+        <v>99</v>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>haribo.com</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>HARIBO</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>john.veidt@haribo.com</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Veidt</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>executive</t>
+        </is>
+      </c>
+      <c r="H628" t="n">
+        <v>99</v>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26245,7 +31845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27704,6 +33304,872 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>welchsfruitsnacks.com</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Welch's® Fruit Snacks</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>mars.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>No executive emails found</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>mondelezinternational.com</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Mondelēz International</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>thehersheycompany.com</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>kelloggs.com</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kellogg's</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>conagrabrands.com</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>nestleusa.com</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nestlé USA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>campbellsoupcompany.com</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Campbell Soup Company</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cheetos.com</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>pringles.com</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pringles</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>doritos.com</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Herreid Super Stop</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>lays.com</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lay's</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>tostitos.com</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TOSTITOS®</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ruffles.com</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ruffles</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>oreo.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>OREO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ritzcrackers.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>RitzCrackers</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>pop-tarts.com</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cheezits.com</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>thegoodbean.com</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>The Good Bean</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>haldirams.com</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Haldirams</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>No executive emails found</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>bettermade.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Better Made Snacks</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>capecodchips.com</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cape Cod Chips</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>naturevalley.com</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Nature Valley</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>baresnacks.com</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Bare Snacks</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>piratesbooty.com</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>reeses.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>REESE'S</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>mms.com</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>M&amp;M's</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>No executive emails found</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>snickers.com</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SNICKERS Ice Cream</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>twix.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TWIX US</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>milka.com</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Milka</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>daim.com</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>No executive emails found</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>trolli.com</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Trolli</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>No emails in database</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>takis.com</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TAKIS-COM</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sasha</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>No executive emails found</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-03-04 16:30:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
